--- a/data/trans_orig/IP12-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP12-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20484</t>
+          <t>20401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42664</t>
+          <t>42483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49855</t>
+          <t>49853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>46988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55485</t>
+          <t>56007</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92301</t>
+          <t>92384</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104240</t>
+          <t>103850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16019</t>
+          <t>15442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>9947</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>22895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85543</t>
+          <t>86120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95323</t>
+          <t>95450</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98350</t>
+          <t>98810</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106235</t>
+          <t>106105</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186983</t>
+          <t>187424</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199277</t>
+          <t>199607</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60574</t>
+          <t>59318</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66818</t>
+          <t>66798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63712</t>
+          <t>63438</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69089</t>
+          <t>69100</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127309</t>
+          <t>127424</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135268</t>
+          <t>135210</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>14029</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21681</t>
+          <t>21252</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63848</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71690</t>
+          <t>71462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66356</t>
+          <t>65082</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74578</t>
+          <t>74643</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132291</t>
+          <t>132720</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144767</t>
+          <t>144081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37705</t>
+          <t>37203</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41473</t>
+          <t>41474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81251</t>
+          <t>81736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86070</t>
+          <t>86076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48039</t>
+          <t>48635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54669</t>
+          <t>54694</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52852</t>
+          <t>53313</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58500</t>
+          <t>58541</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104393</t>
+          <t>104150</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112638</t>
+          <t>112450</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8567</t>
+          <t>8195</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>114260</t>
+          <t>115686</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124379</t>
+          <t>124556</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127088</t>
+          <t>127460</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>134280</t>
+          <t>133720</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>246285</t>
+          <t>246475</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>257452</t>
+          <t>257448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9237</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20667</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28356</t>
+          <t>28197</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>147704</t>
+          <t>147742</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154909</t>
+          <t>155402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>143391</t>
+          <t>142480</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>154821</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>293606</t>
+          <t>293765</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>307680</t>
+          <t>307568</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>34365</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55048</t>
+          <t>55556</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38030</t>
+          <t>37521</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57921</t>
+          <t>58690</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>76515</t>
+          <t>78269</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>107244</t>
+          <t>107397</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>625973</t>
+          <t>625465</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>646732</t>
+          <t>646656</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>664779</t>
+          <t>664010</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>684670</t>
+          <t>685179</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1296477</t>
+          <t>1296324</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1327206</t>
+          <t>1325452</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13586</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47545</t>
+          <t>47477</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55292</t>
+          <t>55505</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51223</t>
+          <t>50506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60554</t>
+          <t>60255</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101780</t>
+          <t>101669</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114205</t>
+          <t>114253</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>18235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8830</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>21687</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>19430</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35446</t>
+          <t>34860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86493</t>
+          <t>86478</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96770</t>
+          <t>97284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91096</t>
+          <t>89472</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102329</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>180426</t>
+          <t>181012</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>196330</t>
+          <t>196442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10453</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>22307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55143</t>
+          <t>54565</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63923</t>
+          <t>63912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58870</t>
+          <t>58703</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67611</t>
+          <t>67738</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116358</t>
+          <t>117125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128979</t>
+          <t>129689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>11663</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22014</t>
+          <t>22101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63969</t>
+          <t>63459</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73180</t>
+          <t>72875</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70695</t>
+          <t>70571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79636</t>
+          <t>79239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137981</t>
+          <t>137894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150827</t>
+          <t>150296</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>10746</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21176</t>
+          <t>21294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30464</t>
+          <t>30217</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39344</t>
+          <t>39330</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35743</t>
+          <t>36006</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43378</t>
+          <t>43550</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69477</t>
+          <t>69359</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81527</t>
+          <t>81189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,56%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>10038</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15783</t>
+          <t>16758</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46153</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53775</t>
+          <t>53784</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51048</t>
+          <t>50207</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58084</t>
+          <t>58110</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100447</t>
+          <t>99472</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110630</t>
+          <t>109721</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12117</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11179</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20477</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>126601</t>
+          <t>126725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>135256</t>
+          <t>135308</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134560</t>
+          <t>134513</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143032</t>
+          <t>143204</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>263980</t>
+          <t>264309</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>276345</t>
+          <t>276657</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>11852</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>16847</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24764</t>
+          <t>25777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>152844</t>
+          <t>152856</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>161407</t>
+          <t>161057</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>155068</t>
+          <t>154468</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>165544</t>
+          <t>164981</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>311259</t>
+          <t>310246</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>324538</t>
+          <t>324366</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>49428</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>74651</t>
+          <t>74848</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>51223</t>
+          <t>52770</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76314</t>
+          <t>77354</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>107969</t>
+          <t>107955</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>145150</t>
+          <t>144490</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>636740</t>
+          <t>636543</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>661204</t>
+          <t>661963</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>677193</t>
+          <t>676153</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>700737</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1319748</t>
+          <t>1320408</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1356929</t>
+          <t>1356943</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14285</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16362</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>13437</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26656</t>
+          <t>26936</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43086</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>52290</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48100</t>
+          <t>48834</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58445</t>
+          <t>58775</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95177</t>
+          <t>94897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108812</t>
+          <t>108396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>15341</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>13816</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25205</t>
+          <t>25278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87855</t>
+          <t>88606</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98274</t>
+          <t>98166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97392</t>
+          <t>96467</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106112</t>
+          <t>105690</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189025</t>
+          <t>188952</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>202346</t>
+          <t>202002</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>7808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60814</t>
+          <t>61295</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66169</t>
+          <t>66183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65163</t>
+          <t>65778</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129440</t>
+          <t>128928</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135410</t>
+          <t>135338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16455</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27874</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60585</t>
+          <t>60854</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71051</t>
+          <t>70885</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64729</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75400</t>
+          <t>75120</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130271</t>
+          <t>130448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144761</t>
+          <t>144320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,26%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>8419</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>544</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11434</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34815</t>
+          <t>35019</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41486</t>
+          <t>41586</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41452</t>
+          <t>41780</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45801</t>
+          <t>45806</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78354</t>
+          <t>79356</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86662</t>
+          <t>86670</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,44 +9134,44 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
+          <t>6059</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2495</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
           <t>6964</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>12,06%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2495</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>6752</t>
-        </is>
-      </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
           <t>2,23%</t>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50367</t>
+          <t>49964</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50775</t>
+          <t>51680</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105260</t>
+          <t>105048</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111295</t>
+          <t>111288</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6732</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>17640</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>126560</t>
+          <t>126907</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>134508</t>
+          <t>134755</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134584</t>
+          <t>133999</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142006</t>
+          <t>142030</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>263894</t>
+          <t>263806</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274844</t>
+          <t>274714</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19736</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5911</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>16450</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31871</t>
+          <t>31507</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143823</t>
+          <t>143482</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154762</t>
+          <t>154660</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>154812</t>
+          <t>154399</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>164938</t>
+          <t>164319</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>302537</t>
+          <t>302901</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>316805</t>
+          <t>317124</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>44576</t>
+          <t>44619</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>67704</t>
+          <t>68026</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38826</t>
+          <t>38294</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61026</t>
+          <t>60359</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>90269</t>
+          <t>89092</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>121541</t>
+          <t>121457</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>636050</t>
+          <t>635728</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>659178</t>
+          <t>659135</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>683818</t>
+          <t>684485</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>706018</t>
+          <t>706550</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1327057</t>
+          <t>1327141</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1358329</t>
+          <t>1359506</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13450</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66076</t>
+          <t>65020</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72412</t>
+          <t>72019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69645</t>
+          <t>70433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78580</t>
+          <t>78564</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139198</t>
+          <t>139866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149665</t>
+          <t>149789</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>15768</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>14061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25849</t>
+          <t>25785</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>110687</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122713</t>
+          <t>122849</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113310</t>
+          <t>113535</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>123728</t>
+          <t>123822</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228586</t>
+          <t>228650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>243707</t>
+          <t>244338</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>11320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>18735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46958</t>
+          <t>47387</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54984</t>
+          <t>54925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56346</t>
+          <t>55843</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64552</t>
+          <t>64522</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106994</t>
+          <t>106696</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>118117</t>
+          <t>117918</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15743</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>20583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61299</t>
+          <t>61520</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68614</t>
+          <t>68696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62391</t>
+          <t>63272</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75695</t>
+          <t>76229</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127264</t>
+          <t>127695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142896</t>
+          <t>142450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27662</t>
+          <t>28004</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33066</t>
+          <t>33000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34840</t>
+          <t>34153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39683</t>
+          <t>39653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64679</t>
+          <t>64416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71807</t>
+          <t>71984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7844</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>20449</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>37945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44253</t>
+          <t>44312</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40741</t>
+          <t>40883</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49828</t>
+          <t>50313</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81892</t>
+          <t>81904</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92927</t>
+          <t>92848</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18221</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22569</t>
+          <t>22219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18018</t>
+          <t>18850</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35173</t>
+          <t>36351</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106287</t>
+          <t>106590</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>116712</t>
+          <t>117212</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>133443</t>
+          <t>133793</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147577</t>
+          <t>147655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>245347</t>
+          <t>244169</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>262502</t>
+          <t>261670</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19568</t>
+          <t>19755</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123601</t>
+          <t>123803</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129669</t>
+          <t>129670</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>142030</t>
+          <t>141953</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152023</t>
+          <t>151956</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>268846</t>
+          <t>268659</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>280327</t>
+          <t>280377</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35978</t>
+          <t>37016</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59317</t>
+          <t>58539</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47607</t>
+          <t>45885</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74856</t>
+          <t>72733</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>89665</t>
+          <t>90023</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>127135</t>
+          <t>125932</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>606023</t>
+          <t>606801</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>629362</t>
+          <t>628324</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>687116</t>
+          <t>689239</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>714365</t>
+          <t>716087</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1300177</t>
+          <t>1301380</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1337647</t>
+          <t>1337289</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
